--- a/artfynd/A 43197-2023 artfynd.xlsx
+++ b/artfynd/A 43197-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43197-2023 artfynd.xlsx
+++ b/artfynd/A 43197-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>95817846</v>
       </c>
       <c r="B2" t="n">
-        <v>77329</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>709267.2563315909</v>
+        <v>709267</v>
       </c>
       <c r="R2" t="n">
-        <v>6399598.48006659</v>
+        <v>6399598</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-07-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,12 +795,7 @@
         <v>111209152</v>
       </c>
       <c r="B3" t="n">
-        <v>96326</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>708946.6915113158</v>
+        <v>708947</v>
       </c>
       <c r="R3" t="n">
-        <v>6399447.445967926</v>
+        <v>6399447</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -929,15 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111209138</v>
+        <v>111209371</v>
       </c>
       <c r="B4" t="n">
-        <v>95532</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -973,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>708946.6915113158</v>
+        <v>709109</v>
       </c>
       <c r="R4" t="n">
-        <v>6399447.445967926</v>
+        <v>6399537</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1023,7 +998,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I kalkbarrskog kontinuitetsskog.</t>
+          <t>I kalkbarrskog med inslag av hassel och brakved Kontinuitetsskog. Partivis fuktig mark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,12 +1029,7 @@
         <v>111209289</v>
       </c>
       <c r="B5" t="n">
-        <v>106989</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>708946.6915113158</v>
+        <v>708947</v>
       </c>
       <c r="R5" t="n">
-        <v>6399447.445967926</v>
+        <v>6399447</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1170,6 +1140,357 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111209428</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bro Tauer, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>709109</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6399537</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I kalkbarrskog med inslag av hassel och björk. Kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111209448</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bro Tauer, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>709109</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6399537</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I kalkbarrskog med inslag av hassel och björk. Kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111209138</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bro Tauer, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>708947</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6399447</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I kalkbarrskog kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43197-2023 artfynd.xlsx
+++ b/artfynd/A 43197-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95817846</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111209152</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111209371</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111209289</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111209428</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111209448</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1491,8 +1526,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111209138</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>